--- a/measurements/30/Filled_2D_sections/axial/week30_axial_Batch_Allmarks.xlsx
+++ b/measurements/30/Filled_2D_sections/axial/week30_axial_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AH29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,107 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,43 +601,73 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.722784057108864</v>
+        <v>3706.122448979591</v>
       </c>
       <c r="D2" t="n">
-        <v>20.11727358364477</v>
+        <v>392.7658175854456</v>
       </c>
       <c r="E2" t="n">
-        <v>13.70174730987084</v>
+        <v>267.5103046212877</v>
       </c>
       <c r="F2" t="n">
         <v>1.468226871265692</v>
       </c>
       <c r="G2" t="n">
-        <v>0.301899406999752</v>
+        <v>0.3018994069997519</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5079077743902439</v>
+        <v>1.726190476190476</v>
       </c>
       <c r="J2" t="n">
-        <v>1.280011432926829</v>
+        <v>24.99069940476191</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8282837906504065</v>
-      </c>
-      <c r="N2" t="inlineStr">
+        <v>9.882015306122449</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>24.99069940476191</v>
+      </c>
+      <c r="N2" t="n">
+        <v>13.60677083333333</v>
+      </c>
+      <c r="P2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5.167410714285714</v>
+      </c>
+      <c r="U2" t="n">
+        <v>9.916294642857142</v>
+      </c>
+      <c r="V2" t="n">
+        <v>7.212611607142857</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.726190476190476</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>9.926977989292089</v>
+      <c r="AH2" s="2" t="n">
+        <v>3783.956916099773</v>
       </c>
     </row>
     <row r="3">
@@ -553,17 +678,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9.795359904818561</v>
+        <v>3733.786848072562</v>
       </c>
       <c r="D3" t="n">
-        <v>19.82805736471967</v>
+        <v>387.1192152159554</v>
       </c>
       <c r="E3" t="n">
-        <v>13.71603478164208</v>
+        <v>267.7892504987262</v>
       </c>
       <c r="F3" t="n">
         <v>1.445611481771546</v>
@@ -572,24 +697,54 @@
         <v>0.3130905274677861</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5625</v>
+        <v>2.016369047619047</v>
       </c>
       <c r="J3" t="n">
-        <v>1.277915396341464</v>
+        <v>24.94977678571428</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8460683434959351</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>9.896364795918368</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>24.94977678571428</v>
+      </c>
+      <c r="N3" t="n">
+        <v>13.6235119047619</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4.430803571428571</v>
+      </c>
+      <c r="U3" t="n">
+        <v>10.98214285714286</v>
+      </c>
+      <c r="V3" t="n">
+        <v>7.171223958333332</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.016369047619047</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>18.37922463795034</v>
+      <c r="AH3" s="2" t="n">
+        <v>358.8324810266494</v>
       </c>
     </row>
     <row r="4">
@@ -600,17 +755,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.834027364663891</v>
+        <v>3748.526077097506</v>
       </c>
       <c r="D4" t="n">
-        <v>19.79948239791684</v>
+        <v>386.5613230069478</v>
       </c>
       <c r="E4" t="n">
-        <v>13.73624032881202</v>
+        <v>268.1837397529965</v>
       </c>
       <c r="F4" t="n">
         <v>1.441404774812149</v>
@@ -619,24 +774,57 @@
         <v>0.3152343990014613</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5846036585365854</v>
+        <v>1.402529761904762</v>
       </c>
       <c r="J4" t="n">
-        <v>1.230564024390244</v>
+        <v>24.02529761904762</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8214240345528455</v>
-      </c>
-      <c r="N4" t="inlineStr">
+        <v>8.749767485119047</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>24.02529761904762</v>
+      </c>
+      <c r="N4" t="n">
+        <v>12.67299107142857</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4.447544642857142</v>
+      </c>
+      <c r="U4" t="n">
+        <v>11.41369047619048</v>
+      </c>
+      <c r="V4" t="n">
+        <v>7.306082589285714</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.672991071428571</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.402529761904762</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>13.32096722314997</v>
+      <c r="AH4" s="2" t="n">
+        <v>260.07602673769</v>
       </c>
     </row>
     <row r="5">
@@ -647,42 +835,75 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9.879833432480666</v>
+        <v>3765.986394557823</v>
       </c>
       <c r="D5" t="n">
-        <v>19.84826290898207</v>
+        <v>387.5137044134594</v>
       </c>
       <c r="E5" t="n">
-        <v>13.78502080789426</v>
+        <v>269.1361205350785</v>
       </c>
       <c r="F5" t="n">
-        <v>1.439842796437099</v>
+        <v>1.439842796437098</v>
       </c>
       <c r="G5" t="n">
         <v>0.3151479445059199</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5867949695121951</v>
+        <v>1.616443452380952</v>
       </c>
       <c r="J5" t="n">
-        <v>1.229706554878049</v>
+        <v>24.00855654761905</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8250127032520326</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>8.738141741071429</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>24.00855654761905</v>
+      </c>
+      <c r="N5" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.950892857142857</v>
+      </c>
+      <c r="U5" t="n">
+        <v>11.45647321428571</v>
+      </c>
+      <c r="V5" t="n">
+        <v>7.120070684523808</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.942708333333333</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.616443452380952</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AH5" s="2" t="n">
         <v>1.379262872622995</v>
       </c>
     </row>
@@ -694,42 +915,78 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10.00237953599048</v>
+        <v>3812.698412698413</v>
       </c>
       <c r="D6" t="n">
-        <v>19.36536072230921</v>
+        <v>378.0856141022273</v>
       </c>
       <c r="E6" t="n">
-        <v>13.675623707655</v>
+        <v>267.00027238755</v>
       </c>
       <c r="F6" t="n">
-        <v>1.416049544524199</v>
+        <v>1.4160495445242</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3351675860392464</v>
+        <v>0.3351675860392463</v>
       </c>
       <c r="H6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.787574404761905</v>
+      </c>
+      <c r="J6" t="n">
+        <v>24.03087797619047</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8.709542410714283</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>24.03087797619047</v>
+      </c>
+      <c r="N6" t="n">
+        <v>12.38095238095238</v>
+      </c>
+      <c r="P6" t="n">
         <v>3</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.5890815548780488</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.230849847560976</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.8180259146341463</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="Q6" t="n">
+        <v>11.50111607142857</v>
+      </c>
+      <c r="R6" t="n">
+        <v>9.010416666666666</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4.31547619047619</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.513764880952381</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.136160714285714</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.787574404761905</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="AH6" s="2" t="n">
         <v>0.3724868059721912</v>
       </c>
     </row>
@@ -741,17 +998,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10.17013682331945</v>
+        <v>3876.643990929705</v>
       </c>
       <c r="D7" t="n">
-        <v>18.32566761679766</v>
+        <v>357.7868439470018</v>
       </c>
       <c r="E7" t="n">
-        <v>13.4829530890395</v>
+        <v>263.2386079288664</v>
       </c>
       <c r="F7" t="n">
         <v>1.359173134830149</v>
@@ -760,24 +1017,57 @@
         <v>0.3805546642650889</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5066692073170732</v>
+        <v>1.919642857142857</v>
       </c>
       <c r="J7" t="n">
-        <v>1.230373475609756</v>
+        <v>24.02157738095238</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7903963414634148</v>
-      </c>
-      <c r="N7" t="inlineStr">
+        <v>7.20796130952381</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>24.02157738095238</v>
+      </c>
+      <c r="N7" t="n">
+        <v>12.38095238095238</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>9.892113095238095</v>
+      </c>
+      <c r="R7" t="n">
+        <v>4.523809523809524</v>
+      </c>
+      <c r="W7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.919642857142857</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3.852306547619047</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.81063988095238</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>2.55</v>
+      <c r="AH7" s="2" t="n">
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -788,17 +1078,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10.19006543723974</v>
+        <v>3884.240362811791</v>
       </c>
       <c r="D8" t="n">
-        <v>18.70509076409224</v>
+        <v>365.1946292037055</v>
       </c>
       <c r="E8" t="n">
-        <v>13.46866563180598</v>
+        <v>262.9596623352596</v>
       </c>
       <c r="F8" t="n">
         <v>1.388785739837549</v>
@@ -807,24 +1097,60 @@
         <v>0.3659882959112727</v>
       </c>
       <c r="H8" t="n">
+        <v>9</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.020089285714286</v>
+      </c>
+      <c r="J8" t="n">
+        <v>23.80952380952381</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7.392113095238096</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>23.80952380952381</v>
+      </c>
+      <c r="N8" t="n">
+        <v>12.38095238095238</v>
+      </c>
+      <c r="P8" t="n">
         <v>3</v>
       </c>
-      <c r="I8" t="n">
-        <v>0.5765053353658537</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.219512195121951</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.8100546239837398</v>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="Q8" t="n">
+        <v>11.25558035714286</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4.172247023809524</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.947172619047619</v>
+      </c>
+      <c r="W8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.020089285714286</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>3.405877976190476</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.740885416666666</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.660618330792683</v>
+      <c r="AH8" s="2" t="n">
+        <v>1.587704613095238</v>
       </c>
     </row>
     <row r="9">
@@ -835,43 +1161,76 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10.16121356335515</v>
+        <v>3873.242630385487</v>
       </c>
       <c r="D9" t="n">
-        <v>18.71937824749365</v>
+        <v>365.4735753082094</v>
       </c>
       <c r="E9" t="n">
-        <v>13.43417261867988</v>
+        <v>262.2862273170834</v>
       </c>
       <c r="F9" t="n">
         <v>1.393415045260385</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3643951631137309</v>
+        <v>0.364395163113731</v>
       </c>
       <c r="H9" t="n">
+        <v>9</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.808035714285714</v>
+      </c>
+      <c r="J9" t="n">
+        <v>24.11830357142857</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7.47829861111111</v>
+      </c>
+      <c r="L9" t="n">
         <v>3</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.6100419207317074</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.235327743902439</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.8265053353658537</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="M9" t="n">
+        <v>24.11830357142857</v>
+      </c>
+      <c r="N9" t="n">
+        <v>12.38095238095238</v>
+      </c>
+      <c r="O9" t="n">
+        <v>11.91034226190476</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="W9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.808035714285714</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>3.802083333333333</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.921875</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>1.338810022865854</v>
+      <c r="AH9" s="2" t="n">
+        <v>26.138671875</v>
       </c>
     </row>
     <row r="10">
@@ -882,17 +1241,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10.13355145746579</v>
+        <v>3862.698412698413</v>
       </c>
       <c r="D10" t="n">
-        <v>18.66467970173533</v>
+        <v>364.4056513195946</v>
       </c>
       <c r="E10" t="n">
-        <v>13.43417261577234</v>
+        <v>262.2862272603171</v>
       </c>
       <c r="F10" t="n">
         <v>1.389343447904052</v>
@@ -901,24 +1260,57 @@
         <v>0.3655362550042352</v>
       </c>
       <c r="H10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.170014880952381</v>
+      </c>
+      <c r="J10" t="n">
+        <v>24.12760416666666</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.813244047619047</v>
+      </c>
+      <c r="L10" t="n">
         <v>3</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.6341463414634146</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.235804115853659</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.8367632113821138</v>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="M10" t="n">
+        <v>24.12760416666666</v>
+      </c>
+      <c r="N10" t="n">
+        <v>12.50186011904762</v>
+      </c>
+      <c r="O10" t="n">
+        <v>12.38095238095238</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.971354166666667</v>
+      </c>
+      <c r="W10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.170014880952381</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>3.532366071428571</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.525111607142857</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9508018927845528</v>
+      <c r="AH10" s="2" t="n">
+        <v>7.665792699260891</v>
       </c>
     </row>
     <row r="11">
@@ -929,17 +1321,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10.09964306960143</v>
+        <v>3849.773242630385</v>
       </c>
       <c r="D11" t="n">
-        <v>18.38873559091149</v>
+        <v>359.0181710606529</v>
       </c>
       <c r="E11" t="n">
-        <v>13.53418495306155</v>
+        <v>264.2388490835825</v>
       </c>
       <c r="F11" t="n">
         <v>1.358688066897727</v>
@@ -948,16 +1340,57 @@
         <v>0.3753290273458919</v>
       </c>
       <c r="H11" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.225818452380952</v>
+      </c>
+      <c r="J11" t="n">
+        <v>24.89769345238095</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.944754464285714</v>
+      </c>
+      <c r="L11" t="n">
         <v>3</v>
       </c>
-      <c r="I11" t="n">
-        <v>0.6256669207317074</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.275247713414634</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.8449250508130083</v>
+      <c r="M11" t="n">
+        <v>24.89769345238095</v>
+      </c>
+      <c r="N11" t="n">
+        <v>12.37537202380952</v>
+      </c>
+      <c r="O11" t="n">
+        <v>12.21540178571428</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.557291666666666</v>
+      </c>
+      <c r="W11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.225818452380952</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>3.603050595238095</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.566964285714286</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AH11" s="2" t="n">
+        <v>2.2</v>
       </c>
     </row>
     <row r="12">
@@ -968,17 +1401,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10.01814396192743</v>
+        <v>3818.707482993197</v>
       </c>
       <c r="D12" t="n">
-        <v>18.8395961319528</v>
+        <v>367.8206863857451</v>
       </c>
       <c r="E12" t="n">
-        <v>13.65541818083786</v>
+        <v>266.605783530644</v>
       </c>
       <c r="F12" t="n">
         <v>1.379642562568292</v>
@@ -987,16 +1420,57 @@
         <v>0.3546940925061589</v>
       </c>
       <c r="H12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.741071428571428</v>
+      </c>
+      <c r="J12" t="n">
+        <v>25.36272321428571</v>
+      </c>
+      <c r="K12" t="n">
+        <v>7.565724206349207</v>
+      </c>
+      <c r="L12" t="n">
         <v>3</v>
       </c>
-      <c r="I12" t="n">
-        <v>0.618235518292683</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.29906631097561</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.8475609756097561</v>
+      <c r="M12" t="n">
+        <v>25.36272321428571</v>
+      </c>
+      <c r="N12" t="n">
+        <v>12.20982142857143</v>
+      </c>
+      <c r="O12" t="n">
+        <v>12.0703125</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.8671875</v>
+      </c>
+      <c r="W12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.741071428571428</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>3.636532738095238</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.916294642857143</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AH12" s="2" t="n">
+        <v>26.138671875</v>
       </c>
     </row>
     <row r="13">
@@ -1007,17 +1481,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10.08863771564545</v>
+        <v>3845.578231292517</v>
       </c>
       <c r="D13" t="n">
-        <v>17.49783533666192</v>
+        <v>341.6244041919708</v>
       </c>
       <c r="E13" t="n">
-        <v>13.51152805874987</v>
+        <v>263.7965001946404</v>
       </c>
       <c r="F13" t="n">
         <v>1.295030085463248</v>
@@ -1026,16 +1500,57 @@
         <v>0.4140699750591719</v>
       </c>
       <c r="H13" t="n">
+        <v>9</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.941964285714286</v>
+      </c>
+      <c r="J13" t="n">
+        <v>25.37388392857143</v>
+      </c>
+      <c r="K13" t="n">
+        <v>7.32287533068783</v>
+      </c>
+      <c r="L13" t="n">
         <v>2</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.6733041158536586</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.299637957317073</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.9864710365853659</v>
+      <c r="M13" t="n">
+        <v>25.37388392857143</v>
+      </c>
+      <c r="N13" t="n">
+        <v>13.14546130952381</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>9.616815476190476</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3.882068452380952</v>
+      </c>
+      <c r="W13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.941964285714286</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>3.469122023809524</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.777529761904762</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AH13" s="2" t="n">
+        <v>13.61662946428571</v>
       </c>
     </row>
     <row r="14">
@@ -1046,35 +1561,73 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10.05472932778108</v>
+        <v>3832.65306122449</v>
       </c>
       <c r="D14" t="n">
-        <v>17.46926035532137</v>
+        <v>341.0665116991315</v>
       </c>
       <c r="E14" t="n">
-        <v>13.33661165179276</v>
+        <v>260.3814655826205</v>
       </c>
       <c r="F14" t="n">
         <v>1.309872463218428</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4140294303609604</v>
+        <v>0.4140294303609606</v>
       </c>
       <c r="H14" t="n">
+        <v>9</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.452752976190476</v>
+      </c>
+      <c r="J14" t="n">
+        <v>26.09002976190476</v>
+      </c>
+      <c r="K14" t="n">
+        <v>7.241236772486772</v>
+      </c>
+      <c r="L14" t="n">
         <v>2</v>
       </c>
-      <c r="I14" t="n">
-        <v>0.6724466463414634</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.336318597560976</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1.00438262195122</v>
+      <c r="M14" t="n">
+        <v>26.09002976190476</v>
+      </c>
+      <c r="N14" t="n">
+        <v>13.12872023809524</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>9.194568452380953</v>
+      </c>
+      <c r="W14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.452752976190476</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>3.629092261904762</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.79296875</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AH14" s="2" t="n">
+        <v>12.14425223214285</v>
       </c>
     </row>
     <row r="15">
@@ -1085,17 +1638,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10.03212373587151</v>
+        <v>3824.036281179138</v>
       </c>
       <c r="D15" t="n">
-        <v>17.45252156257629</v>
+        <v>340.7397066979181</v>
       </c>
       <c r="E15" t="n">
-        <v>13.19027021163847</v>
+        <v>257.5243231796083</v>
       </c>
       <c r="F15" t="n">
         <v>1.323136014846535</v>
@@ -1104,16 +1657,54 @@
         <v>0.4138913762368488</v>
       </c>
       <c r="H15" t="n">
+        <v>9</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.2109375</v>
+      </c>
+      <c r="J15" t="n">
+        <v>26.10491071428571</v>
+      </c>
+      <c r="K15" t="n">
+        <v>7.161665013227513</v>
+      </c>
+      <c r="L15" t="n">
         <v>2</v>
       </c>
-      <c r="I15" t="n">
-        <v>0.6829268292682927</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.337080792682927</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1.01000381097561</v>
+      <c r="M15" t="n">
+        <v>26.10491071428571</v>
+      </c>
+      <c r="N15" t="n">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>8.69047619047619</v>
+      </c>
+      <c r="W15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.2109375</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>3.694196428571428</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.721044146825397</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AH15" s="2" t="n">
+        <v>2.35</v>
       </c>
     </row>
     <row r="16">
@@ -1124,35 +1715,73 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9.992266508030934</v>
+        <v>3808.843537414966</v>
       </c>
       <c r="D16" t="n">
-        <v>17.16820808154781</v>
+        <v>335.1888244492667</v>
       </c>
       <c r="E16" t="n">
-        <v>13.05229815331901</v>
+        <v>254.8305829933711</v>
       </c>
       <c r="F16" t="n">
         <v>1.315339864281462</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4260140633581881</v>
+        <v>0.4260140633581882</v>
       </c>
       <c r="H16" t="n">
+        <v>10</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.313244047619047</v>
+      </c>
+      <c r="J16" t="n">
+        <v>26.57924107142857</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6.538876488095238</v>
+      </c>
+      <c r="L16" t="n">
         <v>2</v>
       </c>
-      <c r="I16" t="n">
-        <v>0.7560975609756098</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.361375762195122</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1.058736661585366</v>
+      <c r="M16" t="n">
+        <v>26.57924107142857</v>
+      </c>
+      <c r="N16" t="n">
+        <v>14.76190476190476</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5.790550595238095</v>
+      </c>
+      <c r="W16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.313244047619047</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>3.584449404761905</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.608152636054421</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AH16" s="2" t="n">
+        <v>6.85999503968254</v>
       </c>
     </row>
     <row r="17">
@@ -1163,17 +1792,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9.870910172516361</v>
+        <v>3762.585034013605</v>
       </c>
       <c r="D17" t="n">
-        <v>16.998194325261</v>
+        <v>331.8695082550957</v>
       </c>
       <c r="E17" t="n">
-        <v>12.87983307024328</v>
+        <v>251.4634075618926</v>
       </c>
       <c r="F17" t="n">
         <v>1.319752688762133</v>
@@ -1182,16 +1811,57 @@
         <v>0.4293005887714272</v>
       </c>
       <c r="H17" t="n">
+        <v>10</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.493675595238095</v>
+      </c>
+      <c r="J17" t="n">
+        <v>27.67671130952381</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6.359374999999998</v>
+      </c>
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.7486661585365854</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.417587652439025</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1.083126905487805</v>
+      <c r="M17" t="n">
+        <v>27.67671130952381</v>
+      </c>
+      <c r="N17" t="n">
+        <v>14.61681547619047</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4.267113095238095</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3.740699404761905</v>
+      </c>
+      <c r="W17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.493675595238095</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>3.407738095238095</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.215401785714286</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AH17" s="2" t="n">
+        <v>4.72958519345238</v>
       </c>
     </row>
     <row r="18">
@@ -1202,35 +1872,79 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9.789708506841166</v>
+        <v>3731.632653061224</v>
       </c>
       <c r="D18" t="n">
-        <v>17.16228998870384</v>
+        <v>335.0732807318369</v>
       </c>
       <c r="E18" t="n">
-        <v>12.83697065202201</v>
+        <v>250.6265698728107</v>
       </c>
       <c r="F18" t="n">
         <v>1.336942371680232</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4176660286719884</v>
+        <v>0.4176660286719885</v>
       </c>
       <c r="H18" t="n">
+        <v>9</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.610863095238095</v>
+      </c>
+      <c r="J18" t="n">
+        <v>27.8422619047619</v>
+      </c>
+      <c r="K18" t="n">
+        <v>7.112475198412698</v>
+      </c>
+      <c r="L18" t="n">
         <v>2</v>
       </c>
-      <c r="I18" t="n">
-        <v>0.7712461890243902</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.426067073170732</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1.098656631097561</v>
+      <c r="M18" t="n">
+        <v>27.8422619047619</v>
+      </c>
+      <c r="N18" t="n">
+        <v>15.05766369047619</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.845610119047619</v>
+      </c>
+      <c r="R18" t="n">
+        <v>3.976934523809524</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.971354166666667</v>
+      </c>
+      <c r="W18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.610863095238095</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.587425595238095</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.079613095238095</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AH18" s="2" t="n">
+        <v>3.950892857142857</v>
       </c>
     </row>
     <row r="19">
@@ -1241,35 +1955,76 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9.709696609161215</v>
+        <v>3701.133786848072</v>
       </c>
       <c r="D19" t="n">
-        <v>17.2657690397123</v>
+        <v>337.0935860134306</v>
       </c>
       <c r="E19" t="n">
-        <v>12.74777908732251</v>
+        <v>248.8852107524872</v>
       </c>
       <c r="F19" t="n">
         <v>1.35441388821076</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4093018143555012</v>
+        <v>0.4093018143555013</v>
       </c>
       <c r="H19" t="n">
+        <v>9</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.644345238095238</v>
+      </c>
+      <c r="J19" t="n">
+        <v>28.86904761904762</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7.313574735449736</v>
+      </c>
+      <c r="L19" t="n">
         <v>2</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.478658536585366</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1.129573170731707</v>
+      <c r="M19" t="n">
+        <v>28.86904761904762</v>
+      </c>
+      <c r="N19" t="n">
+        <v>15.23809523809524</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>5.238095238095238</v>
+      </c>
+      <c r="R19" t="n">
+        <v>3.947172619047619</v>
+      </c>
+      <c r="W19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.644345238095238</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>3.565848214285714</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.50595238095238</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AH19" s="2" t="n">
+        <v>4.417410714285714</v>
       </c>
     </row>
     <row r="20">
@@ -1280,17 +2035,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9.607079119571685</v>
+        <v>3662.018140589569</v>
       </c>
       <c r="D20" t="n">
-        <v>17.78806688145893</v>
+        <v>347.2908295903887</v>
       </c>
       <c r="E20" t="n">
-        <v>12.71920410598197</v>
+        <v>248.3273182596479</v>
       </c>
       <c r="F20" t="n">
         <v>1.398520436753824</v>
@@ -1299,16 +2054,60 @@
         <v>0.3815432054575517</v>
       </c>
       <c r="H20" t="n">
+        <v>9</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.577380952380952</v>
+      </c>
+      <c r="J20" t="n">
+        <v>30.67150297619047</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7.81229332010582</v>
+      </c>
+      <c r="L20" t="n">
         <v>2</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.8225990853658537</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.570979420731707</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1.19678925304878</v>
+      <c r="M20" t="n">
+        <v>30.67150297619047</v>
+      </c>
+      <c r="N20" t="n">
+        <v>16.06026785714286</v>
+      </c>
+      <c r="P20" t="n">
+        <v>4</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4.090401785714286</v>
+      </c>
+      <c r="U20" t="n">
+        <v>5.1953125</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4.408947172619047</v>
+      </c>
+      <c r="W20" t="n">
+        <v>3</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.269345238095238</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.096354166666667</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.577380952380952</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AH20" s="2" t="n">
+        <v>9.792782738095237</v>
       </c>
     </row>
     <row r="21">
@@ -1319,17 +2118,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>9.387269482450922</v>
+        <v>3578.231292517007</v>
       </c>
       <c r="D21" t="n">
-        <v>18.18076215720758</v>
+        <v>354.9577373550052</v>
       </c>
       <c r="E21" t="n">
-        <v>12.52061544685829</v>
+        <v>244.4501111053285</v>
       </c>
       <c r="F21" t="n">
         <v>1.452066173134449</v>
@@ -1338,16 +2137,60 @@
         <v>0.3568822750116419</v>
       </c>
       <c r="H21" t="n">
+        <v>11</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.07514880952381</v>
+      </c>
+      <c r="J21" t="n">
+        <v>35.22321428571428</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7.075554653679652</v>
+      </c>
+      <c r="L21" t="n">
         <v>2</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.9024390243902439</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1.804115853658537</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1.35327743902439</v>
+      <c r="M21" t="n">
+        <v>35.22321428571428</v>
+      </c>
+      <c r="N21" t="n">
+        <v>17.61904761904762</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>5.926339285714286</v>
+      </c>
+      <c r="R21" t="n">
+        <v>4.583333333333333</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.569568452380952</v>
+      </c>
+      <c r="W21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.07514880952381</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>3.305431547619047</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.818266369047619</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AH21" s="2" t="n">
+        <v>6.643787202380952</v>
       </c>
     </row>
     <row r="22">
@@ -1357,7 +2200,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AH22" s="2" t="n">
+        <v>4.4</v>
       </c>
     </row>
     <row r="23">
@@ -1371,6 +2222,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AH23" s="2" t="n">
+        <v>2.523561507936507</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1380,6 +2239,90 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AH24" s="2" t="n">
+        <v>2.062872023809524</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AH25" s="2" t="n">
+        <v>1.682477678571429</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AH26" s="2" t="n">
+        <v>1.544828869047619</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AH27" s="2" t="n">
+        <v>3.505394345238095</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AH28" s="2" t="n">
+        <v>2.571478554219307</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AH29" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/measurements/30/Filled_2D_sections/axial/week30_axial_Batch_Allmarks.xlsx
+++ b/measurements/30/Filled_2D_sections/axial/week30_axial_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2328,4 +2534,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week30_axial_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>axial</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3783.956916099773</v>
+      </c>
+      <c r="D10" t="n">
+        <v>81.10401643779467</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3578.231292517007</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3884.240362811791</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>358.8324810266495</v>
+      </c>
+      <c r="D11" t="n">
+        <v>19.89680611212813</v>
+      </c>
+      <c r="E11" t="n">
+        <v>331.8695082550957</v>
+      </c>
+      <c r="F11" t="n">
+        <v>392.7658175854456</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.379262872622995</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.05290949790642593</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.295030085463248</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.468226871265692</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.3724868059721912</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.04103840229220688</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3018994069997519</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.4293005887714272</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis2_s00_idx0134.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis2_s01_idx0135.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>7</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>7</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis2_s02_idx0136.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>8</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>8</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis2_s03_idx0137.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>8</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>8</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis2_s04_idx0138.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>8</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis2_s05_idx0140.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>9</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>9</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis2_s06_idx0141.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>9</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>9</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis2_s07_idx0142.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>9</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>9</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis2_s08_idx0143.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>10</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>10</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>6</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis2_s09_idx0144.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>10</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>10</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>6</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis2_s10_idx0146.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>9</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>9</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis2_s11_idx0147.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>9</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>9</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis2_s12_idx0148.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>9</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>9</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>6</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis2_s13_idx0149.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>9</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>9</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>6</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis2_s14_idx0150.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>10</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>7</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>10</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>7</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis2_s15_idx0152.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>10</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>6</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>10</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>6</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis2_s16_idx0153.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>9</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>4</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>9</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" t="n">
+        <v>4</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis2_s17_idx0154.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>9</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>9</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>5</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis2_s18_idx0155.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>9</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>9</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis2_s19_idx0157.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>11</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>6</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>11</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" t="n">
+        <v>6</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.998683343734455</v>
+      </c>
+      <c r="E40" t="n">
+        <v>7</v>
+      </c>
+      <c r="F40" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.4103913408340616</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.225818738210249</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.818038271845435</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>44</v>
+      </c>
+      <c r="C48" t="n">
+        <v>19.17461444805195</v>
+      </c>
+      <c r="D48" t="n">
+        <v>6.786497239429804</v>
+      </c>
+      <c r="E48" t="n">
+        <v>11.91034226190476</v>
+      </c>
+      <c r="F48" t="n">
+        <v>35.22321428571428</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>47</v>
+      </c>
+      <c r="C49" t="n">
+        <v>6.157785587639312</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.538535248434328</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.569568452380952</v>
+      </c>
+      <c r="F49" t="n">
+        <v>11.50111607142857</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>88</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.520419034090909</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.7058947484470054</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.07514880952381</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.852306547619047</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>